--- a/Data_clean/MCAS/Estados_US/Edos_USA_2020/NEW_MEXICO_2020.xlsx
+++ b/Data_clean/MCAS/Estados_US/Edos_USA_2020/NEW_MEXICO_2020.xlsx
@@ -351,28 +351,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D599"/>
+  <dimension ref="A1:D593"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
@@ -395,6 +395,11 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>Calvillo</t>
@@ -408,6 +413,11 @@
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>Cosío</t>
@@ -421,6 +431,11 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>Jesús María</t>
@@ -434,9 +449,14 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Rincón de Romos</t>
+          <t>Rincón De Romos</t>
         </is>
       </c>
       <c r="C6">
@@ -447,6 +467,11 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>Total</t>
@@ -478,6 +503,11 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>Mexicali</t>
@@ -491,6 +521,11 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>Tijuana</t>
@@ -504,6 +539,11 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>Total</t>
@@ -535,6 +575,11 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Baja California Sur</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
           <t>La Paz</t>
@@ -548,6 +593,11 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Baja California Sur</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>Total</t>
@@ -579,6 +629,11 @@
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Campeche</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>Total</t>
@@ -610,6 +665,11 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>Cintalapa</t>
@@ -623,9 +683,14 @@
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Comitán de Domínguez</t>
+          <t>Comitán De Domínguez</t>
         </is>
       </c>
       <c r="C19">
@@ -636,6 +701,11 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>Frontera Comalapa</t>
@@ -649,6 +719,11 @@
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>La Trinitaria</t>
@@ -662,6 +737,11 @@
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>Las Margaritas</t>
@@ -675,6 +755,11 @@
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>Mapastepec</t>
@@ -688,6 +773,11 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
           <t>Mazatán</t>
@@ -701,6 +791,11 @@
       </c>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
           <t>Motozintla</t>
@@ -714,9 +809,14 @@
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ocozocoautla de Espinosa</t>
+          <t>Ocozocoautla De Espinosa</t>
         </is>
       </c>
       <c r="C26">
@@ -727,6 +827,11 @@
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>Palenque</t>
@@ -740,9 +845,14 @@
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>San Cristóbal de las Casas</t>
+          <t>San Cristóbal De Las Casas</t>
         </is>
       </c>
       <c r="C28">
@@ -753,6 +863,11 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>Suchiate</t>
@@ -766,6 +881,11 @@
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
           <t>Tapachula</t>
@@ -779,6 +899,11 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>Tapilula</t>
@@ -792,6 +917,11 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>Tecpatán</t>
@@ -805,6 +935,11 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>Tonalá</t>
@@ -818,6 +953,11 @@
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>Tuxtla Chico</t>
@@ -831,6 +971,11 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
           <t>Tuxtla Gutiérrez</t>
@@ -844,6 +989,11 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
           <t>Tuzantán</t>
@@ -857,6 +1007,11 @@
       </c>
     </row>
     <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
           <t>Villa Comaltitlán</t>
@@ -870,6 +1025,11 @@
       </c>
     </row>
     <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
           <t>Total</t>
@@ -901,6 +1061,11 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>Aldama</t>
@@ -914,6 +1079,11 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>Allende</t>
@@ -927,6 +1097,11 @@
       </c>
     </row>
     <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
           <t>Ascensión</t>
@@ -940,6 +1115,11 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>Bachíniva</t>
@@ -953,6 +1133,11 @@
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
           <t>Balleza</t>
@@ -966,6 +1151,11 @@
       </c>
     </row>
     <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
           <t>Batopilas</t>
@@ -979,6 +1169,11 @@
       </c>
     </row>
     <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B46" t="inlineStr">
         <is>
           <t>Bocoyna</t>
@@ -992,6 +1187,11 @@
       </c>
     </row>
     <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
           <t>Buenaventura</t>
@@ -1005,6 +1205,11 @@
       </c>
     </row>
     <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
           <t>Camargo</t>
@@ -1018,6 +1223,11 @@
       </c>
     </row>
     <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
           <t>Carichí</t>
@@ -1031,6 +1241,11 @@
       </c>
     </row>
     <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
           <t>Casas Grandes</t>
@@ -1044,6 +1259,11 @@
       </c>
     </row>
     <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
           <t>Chihuahua</t>
@@ -1057,6 +1277,11 @@
       </c>
     </row>
     <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
           <t>Chínipas</t>
@@ -1070,6 +1295,11 @@
       </c>
     </row>
     <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
           <t>Coronado</t>
@@ -1083,6 +1313,11 @@
       </c>
     </row>
     <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
           <t>Cuauhtémoc</t>
@@ -1096,6 +1331,11 @@
       </c>
     </row>
     <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
           <t>Cusihuiriachi</t>
@@ -1109,6 +1349,11 @@
       </c>
     </row>
     <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
           <t>Delicias</t>
@@ -1122,6 +1367,11 @@
       </c>
     </row>
     <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B57" t="inlineStr">
         <is>
           <t>Dr. Belisario Domínguez</t>
@@ -1135,6 +1385,11 @@
       </c>
     </row>
     <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
           <t>El Tule</t>
@@ -1148,6 +1403,11 @@
       </c>
     </row>
     <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
           <t>Galeana</t>
@@ -1161,6 +1421,11 @@
       </c>
     </row>
     <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
           <t>Gómez Farías</t>
@@ -1174,6 +1439,11 @@
       </c>
     </row>
     <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
           <t>Gran Morelos</t>
@@ -1187,6 +1457,11 @@
       </c>
     </row>
     <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
           <t>Guachochi</t>
@@ -1200,6 +1475,11 @@
       </c>
     </row>
     <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B63" t="inlineStr">
         <is>
           <t>Guadalupe</t>
@@ -1213,9 +1493,14 @@
       </c>
     </row>
     <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Guadalupe y Calvo</t>
+          <t>Guadalupe Y Calvo</t>
         </is>
       </c>
       <c r="C64">
@@ -1226,6 +1511,11 @@
       </c>
     </row>
     <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr">
         <is>
           <t>Guazapares</t>
@@ -1239,6 +1529,11 @@
       </c>
     </row>
     <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr">
         <is>
           <t>Guerero</t>
@@ -1252,9 +1547,14 @@
       </c>
     </row>
     <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Hidalgo del Parral</t>
+          <t>Hidalgo Del Parral</t>
         </is>
       </c>
       <c r="C67">
@@ -1265,6 +1565,11 @@
       </c>
     </row>
     <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B68" t="inlineStr">
         <is>
           <t>Huejotitán</t>
@@ -1278,6 +1583,11 @@
       </c>
     </row>
     <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
           <t>Ignacio Zaragoza</t>
@@ -1291,6 +1601,11 @@
       </c>
     </row>
     <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
           <t>Janos</t>
@@ -1304,6 +1619,11 @@
       </c>
     </row>
     <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr">
         <is>
           <t>Jiménez</t>
@@ -1317,6 +1637,11 @@
       </c>
     </row>
     <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
           <t>Juárez</t>
@@ -1330,6 +1655,11 @@
       </c>
     </row>
     <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
           <t>Julimes</t>
@@ -1343,6 +1673,11 @@
       </c>
     </row>
     <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
           <t>La Cruz</t>
@@ -1356,6 +1691,11 @@
       </c>
     </row>
     <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B75" t="inlineStr">
         <is>
           <t>López</t>
@@ -1369,6 +1709,11 @@
       </c>
     </row>
     <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
           <t>Madera</t>
@@ -1382,6 +1727,11 @@
       </c>
     </row>
     <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
           <t>Maguarichi</t>
@@ -1395,6 +1745,11 @@
       </c>
     </row>
     <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
           <t>Manuel Benavides</t>
@@ -1408,6 +1763,11 @@
       </c>
     </row>
     <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B79" t="inlineStr">
         <is>
           <t>Matachí</t>
@@ -1421,6 +1781,11 @@
       </c>
     </row>
     <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B80" t="inlineStr">
         <is>
           <t>Matamoros</t>
@@ -1434,6 +1799,11 @@
       </c>
     </row>
     <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B81" t="inlineStr">
         <is>
           <t>Meoqui</t>
@@ -1447,6 +1817,11 @@
       </c>
     </row>
     <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B82" t="inlineStr">
         <is>
           <t>Morelos</t>
@@ -1460,6 +1835,11 @@
       </c>
     </row>
     <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B83" t="inlineStr">
         <is>
           <t>Moris</t>
@@ -1473,6 +1853,11 @@
       </c>
     </row>
     <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B84" t="inlineStr">
         <is>
           <t>Namiquipa</t>
@@ -1486,6 +1871,11 @@
       </c>
     </row>
     <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B85" t="inlineStr">
         <is>
           <t>Nonoava</t>
@@ -1499,6 +1889,11 @@
       </c>
     </row>
     <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B86" t="inlineStr">
         <is>
           <t>Nuevo Casas Grandes</t>
@@ -1512,6 +1907,11 @@
       </c>
     </row>
     <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B87" t="inlineStr">
         <is>
           <t>Ocampo</t>
@@ -1525,6 +1925,11 @@
       </c>
     </row>
     <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B88" t="inlineStr">
         <is>
           <t>Ojinaga</t>
@@ -1538,6 +1943,11 @@
       </c>
     </row>
     <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B89" t="inlineStr">
         <is>
           <t>Praxedis G. Guerero</t>
@@ -1551,6 +1961,11 @@
       </c>
     </row>
     <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B90" t="inlineStr">
         <is>
           <t>Riva Palacio</t>
@@ -1564,6 +1979,11 @@
       </c>
     </row>
     <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B91" t="inlineStr">
         <is>
           <t>Rosales</t>
@@ -1577,6 +1997,11 @@
       </c>
     </row>
     <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B92" t="inlineStr">
         <is>
           <t>Rosario</t>
@@ -1590,9 +2015,14 @@
       </c>
     </row>
     <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>San Francisco de Borja</t>
+          <t>San Francisco De Borja</t>
         </is>
       </c>
       <c r="C93">
@@ -1603,9 +2033,14 @@
       </c>
     </row>
     <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>San Francisco de Conchos</t>
+          <t>San Francisco De Conchos</t>
         </is>
       </c>
       <c r="C94">
@@ -1616,9 +2051,14 @@
       </c>
     </row>
     <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>San Francisco del Oro</t>
+          <t>San Francisco Del Oro</t>
         </is>
       </c>
       <c r="C95">
@@ -1629,6 +2069,11 @@
       </c>
     </row>
     <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B96" t="inlineStr">
         <is>
           <t>Santa Bárbara</t>
@@ -1642,6 +2087,11 @@
       </c>
     </row>
     <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B97" t="inlineStr">
         <is>
           <t>Santa Isabel</t>
@@ -1655,6 +2105,11 @@
       </c>
     </row>
     <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B98" t="inlineStr">
         <is>
           <t>Satevó</t>
@@ -1668,6 +2123,11 @@
       </c>
     </row>
     <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B99" t="inlineStr">
         <is>
           <t>Saucillo</t>
@@ -1681,6 +2141,11 @@
       </c>
     </row>
     <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B100" t="inlineStr">
         <is>
           <t>Temósachic</t>
@@ -1694,6 +2159,11 @@
       </c>
     </row>
     <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B101" t="inlineStr">
         <is>
           <t>Urique</t>
@@ -1707,6 +2177,11 @@
       </c>
     </row>
     <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B102" t="inlineStr">
         <is>
           <t>Uruachi</t>
@@ -1720,9 +2195,14 @@
       </c>
     </row>
     <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Valle de Zaragoza</t>
+          <t>Valle De Zaragoza</t>
         </is>
       </c>
       <c r="C103">
@@ -1733,6 +2213,11 @@
       </c>
     </row>
     <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B104" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1764,6 +2249,11 @@
       </c>
     </row>
     <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B106" t="inlineStr">
         <is>
           <t>Allende</t>
@@ -1777,6 +2267,11 @@
       </c>
     </row>
     <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B107" t="inlineStr">
         <is>
           <t>Escobedo</t>
@@ -1790,6 +2285,11 @@
       </c>
     </row>
     <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B108" t="inlineStr">
         <is>
           <t>Francisco I. Madero</t>
@@ -1803,6 +2303,11 @@
       </c>
     </row>
     <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B109" t="inlineStr">
         <is>
           <t>Hidalgo</t>
@@ -1816,6 +2321,11 @@
       </c>
     </row>
     <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B110" t="inlineStr">
         <is>
           <t>Matamoros</t>
@@ -1829,6 +2339,11 @@
       </c>
     </row>
     <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B111" t="inlineStr">
         <is>
           <t>Monclova</t>
@@ -1842,6 +2357,11 @@
       </c>
     </row>
     <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B112" t="inlineStr">
         <is>
           <t>Morelos</t>
@@ -1855,6 +2375,11 @@
       </c>
     </row>
     <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B113" t="inlineStr">
         <is>
           <t>Múzquiz</t>
@@ -1868,6 +2393,11 @@
       </c>
     </row>
     <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B114" t="inlineStr">
         <is>
           <t>San Pedro</t>
@@ -1881,6 +2411,11 @@
       </c>
     </row>
     <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B115" t="inlineStr">
         <is>
           <t>Torreón</t>
@@ -1894,6 +2429,11 @@
       </c>
     </row>
     <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B116" t="inlineStr">
         <is>
           <t>Viesca</t>
@@ -1907,6 +2447,11 @@
       </c>
     </row>
     <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B117" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1938,6 +2483,11 @@
       </c>
     </row>
     <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B119" t="inlineStr">
         <is>
           <t>Manzanillo</t>
@@ -1951,6 +2501,11 @@
       </c>
     </row>
     <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B120" t="inlineStr">
         <is>
           <t>Tecomán</t>
@@ -1964,6 +2519,11 @@
       </c>
     </row>
     <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B121" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1979,7 +2539,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Ciudad de México</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -1995,6 +2555,11 @@
       </c>
     </row>
     <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B123" t="inlineStr">
         <is>
           <t>Azcapotzalco</t>
@@ -2008,6 +2573,11 @@
       </c>
     </row>
     <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B124" t="inlineStr">
         <is>
           <t>Benito Juárez</t>
@@ -2021,6 +2591,11 @@
       </c>
     </row>
     <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B125" t="inlineStr">
         <is>
           <t>Coyoacán</t>
@@ -2034,6 +2609,11 @@
       </c>
     </row>
     <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B126" t="inlineStr">
         <is>
           <t>Cuauhtémoc</t>
@@ -2047,6 +2627,11 @@
       </c>
     </row>
     <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B127" t="inlineStr">
         <is>
           <t>Gustavo A. Madero</t>
@@ -2060,6 +2645,11 @@
       </c>
     </row>
     <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B128" t="inlineStr">
         <is>
           <t>Iztacalco</t>
@@ -2073,6 +2663,11 @@
       </c>
     </row>
     <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B129" t="inlineStr">
         <is>
           <t>Iztapalapa</t>
@@ -2086,6 +2681,11 @@
       </c>
     </row>
     <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B130" t="inlineStr">
         <is>
           <t>Miguel Hidalgo</t>
@@ -2099,6 +2699,11 @@
       </c>
     </row>
     <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B131" t="inlineStr">
         <is>
           <t>Tláhuac</t>
@@ -2112,6 +2717,11 @@
       </c>
     </row>
     <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B132" t="inlineStr">
         <is>
           <t>Tlalpan</t>
@@ -2125,6 +2735,11 @@
       </c>
     </row>
     <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B133" t="inlineStr">
         <is>
           <t>Venustiano Carranza</t>
@@ -2138,6 +2753,11 @@
       </c>
     </row>
     <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B134" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2169,9 +2789,14 @@
       </c>
     </row>
     <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Coneto de Comonfort</t>
+          <t>Coneto De Comonfort</t>
         </is>
       </c>
       <c r="C136">
@@ -2182,6 +2807,11 @@
       </c>
     </row>
     <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B137" t="inlineStr">
         <is>
           <t>Cuencamé</t>
@@ -2195,6 +2825,11 @@
       </c>
     </row>
     <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B138" t="inlineStr">
         <is>
           <t>Durango</t>
@@ -2208,6 +2843,11 @@
       </c>
     </row>
     <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B139" t="inlineStr">
         <is>
           <t>El Oro</t>
@@ -2221,6 +2861,11 @@
       </c>
     </row>
     <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B140" t="inlineStr">
         <is>
           <t>Gómez Palacio</t>
@@ -2234,6 +2879,11 @@
       </c>
     </row>
     <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B141" t="inlineStr">
         <is>
           <t>General Simón Bolívar</t>
@@ -2247,6 +2897,11 @@
       </c>
     </row>
     <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B142" t="inlineStr">
         <is>
           <t>Guadalupe Victoria</t>
@@ -2260,6 +2915,11 @@
       </c>
     </row>
     <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B143" t="inlineStr">
         <is>
           <t>Guanaceví</t>
@@ -2273,6 +2933,11 @@
       </c>
     </row>
     <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B144" t="inlineStr">
         <is>
           <t>Hidalgo</t>
@@ -2286,6 +2951,11 @@
       </c>
     </row>
     <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B145" t="inlineStr">
         <is>
           <t>Indé</t>
@@ -2299,6 +2969,11 @@
       </c>
     </row>
     <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B146" t="inlineStr">
         <is>
           <t>Lerdo</t>
@@ -2312,6 +2987,11 @@
       </c>
     </row>
     <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B147" t="inlineStr">
         <is>
           <t>Mapimí</t>
@@ -2325,6 +3005,11 @@
       </c>
     </row>
     <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B148" t="inlineStr">
         <is>
           <t>Mezquital</t>
@@ -2338,6 +3023,11 @@
       </c>
     </row>
     <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B149" t="inlineStr">
         <is>
           <t>Nazas</t>
@@ -2351,9 +3041,14 @@
       </c>
     </row>
     <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Nombre de Dios</t>
+          <t>Nombre De Dios</t>
         </is>
       </c>
       <c r="C150">
@@ -2364,6 +3059,11 @@
       </c>
     </row>
     <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B151" t="inlineStr">
         <is>
           <t>Nuevo Ideal</t>
@@ -2377,6 +3077,11 @@
       </c>
     </row>
     <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B152" t="inlineStr">
         <is>
           <t>Ocampo</t>
@@ -2390,9 +3095,14 @@
       </c>
     </row>
     <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Pánuco de Coronado</t>
+          <t>Pánuco De Coronado</t>
         </is>
       </c>
       <c r="C153">
@@ -2403,6 +3113,11 @@
       </c>
     </row>
     <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B154" t="inlineStr">
         <is>
           <t>Peñón Blanco</t>
@@ -2416,6 +3131,11 @@
       </c>
     </row>
     <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B155" t="inlineStr">
         <is>
           <t>Poanas</t>
@@ -2429,6 +3149,11 @@
       </c>
     </row>
     <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B156" t="inlineStr">
         <is>
           <t>Pueblo Nuevo</t>
@@ -2442,6 +3167,11 @@
       </c>
     </row>
     <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B157" t="inlineStr">
         <is>
           <t>Rodeo</t>
@@ -2455,6 +3185,11 @@
       </c>
     </row>
     <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B158" t="inlineStr">
         <is>
           <t>San Bernardo</t>
@@ -2468,6 +3203,11 @@
       </c>
     </row>
     <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B159" t="inlineStr">
         <is>
           <t>San Dimas</t>
@@ -2481,9 +3221,14 @@
       </c>
     </row>
     <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>San Juan del Río</t>
+          <t>San Juan Del Río</t>
         </is>
       </c>
       <c r="C160">
@@ -2494,9 +3239,14 @@
       </c>
     </row>
     <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>San Luis del Cordero</t>
+          <t>San Luis Del Cordero</t>
         </is>
       </c>
       <c r="C161">
@@ -2507,6 +3257,11 @@
       </c>
     </row>
     <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B162" t="inlineStr">
         <is>
           <t>Santa Clara</t>
@@ -2520,6 +3275,11 @@
       </c>
     </row>
     <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B163" t="inlineStr">
         <is>
           <t>Santiago Papasquiaro</t>
@@ -2533,6 +3293,11 @@
       </c>
     </row>
     <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B164" t="inlineStr">
         <is>
           <t>Súchil</t>
@@ -2546,6 +3311,11 @@
       </c>
     </row>
     <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B165" t="inlineStr">
         <is>
           <t>Tepehuanes</t>
@@ -2559,6 +3329,11 @@
       </c>
     </row>
     <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B166" t="inlineStr">
         <is>
           <t>Tlahualilo</t>
@@ -2572,6 +3347,11 @@
       </c>
     </row>
     <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B167" t="inlineStr">
         <is>
           <t>Vicente Guerero</t>
@@ -2585,6 +3365,11 @@
       </c>
     </row>
     <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B168" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2594,18 +3379,18 @@
         <v>346</v>
       </c>
       <c r="D168">
-        <v>0.09293580445876981</v>
+        <v>0.0929358044587698</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Estado de México</t>
+          <t>Estado De México</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Almoloya de Juárez</t>
+          <t>Almoloya De Juárez</t>
         </is>
       </c>
       <c r="C169">
@@ -2616,6 +3401,11 @@
       </c>
     </row>
     <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B170" t="inlineStr">
         <is>
           <t>Atizapán</t>
@@ -2629,6 +3419,11 @@
       </c>
     </row>
     <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B171" t="inlineStr">
         <is>
           <t>Atlacomulco</t>
@@ -2642,6 +3437,11 @@
       </c>
     </row>
     <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B172" t="inlineStr">
         <is>
           <t>Atlautla</t>
@@ -2655,6 +3455,11 @@
       </c>
     </row>
     <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B173" t="inlineStr">
         <is>
           <t>Chalco</t>
@@ -2668,9 +3473,14 @@
       </c>
     </row>
     <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Chapa de Mota</t>
+          <t>Chapa De Mota</t>
         </is>
       </c>
       <c r="C174">
@@ -2681,9 +3491,14 @@
       </c>
     </row>
     <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Coacalco de Berriozábal</t>
+          <t>Coacalco De Berriozábal</t>
         </is>
       </c>
       <c r="C175">
@@ -2694,6 +3509,11 @@
       </c>
     </row>
     <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B176" t="inlineStr">
         <is>
           <t>Coatepec Harinas</t>
@@ -2707,6 +3527,11 @@
       </c>
     </row>
     <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B177" t="inlineStr">
         <is>
           <t>Coyotepec</t>
@@ -2720,9 +3545,14 @@
       </c>
     </row>
     <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Ecatepec de Morelos</t>
+          <t>Ecatepec De Morelos</t>
         </is>
       </c>
       <c r="C178">
@@ -2733,6 +3563,11 @@
       </c>
     </row>
     <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B179" t="inlineStr">
         <is>
           <t>Huehuetoca</t>
@@ -2746,9 +3581,14 @@
       </c>
     </row>
     <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Ixtapan de la Sal</t>
+          <t>Ixtapan De La Sal</t>
         </is>
       </c>
       <c r="C180">
@@ -2759,6 +3599,11 @@
       </c>
     </row>
     <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B181" t="inlineStr">
         <is>
           <t>Ixtlahuaca</t>
@@ -2772,6 +3617,11 @@
       </c>
     </row>
     <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B182" t="inlineStr">
         <is>
           <t>Jilotepec</t>
@@ -2785,6 +3635,11 @@
       </c>
     </row>
     <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B183" t="inlineStr">
         <is>
           <t>Jiquipilco</t>
@@ -2798,9 +3653,14 @@
       </c>
     </row>
     <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Naucalpan de Juárez</t>
+          <t>Naucalpan De Juárez</t>
         </is>
       </c>
       <c r="C184">
@@ -2811,6 +3671,11 @@
       </c>
     </row>
     <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B185" t="inlineStr">
         <is>
           <t>Nezahualcóyotl</t>
@@ -2824,6 +3689,11 @@
       </c>
     </row>
     <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B186" t="inlineStr">
         <is>
           <t>Otzoloapan</t>
@@ -2837,6 +3707,11 @@
       </c>
     </row>
     <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B187" t="inlineStr">
         <is>
           <t>Polotitlán</t>
@@ -2850,9 +3725,14 @@
       </c>
     </row>
     <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>San Felipe del Progreso</t>
+          <t>San Felipe Del Progreso</t>
         </is>
       </c>
       <c r="C188">
@@ -2863,6 +3743,11 @@
       </c>
     </row>
     <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B189" t="inlineStr">
         <is>
           <t>Tecámac</t>
@@ -2876,6 +3761,11 @@
       </c>
     </row>
     <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B190" t="inlineStr">
         <is>
           <t>Tejupilco</t>
@@ -2889,6 +3779,11 @@
       </c>
     </row>
     <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B191" t="inlineStr">
         <is>
           <t>Temascalcingo</t>
@@ -2902,6 +3797,11 @@
       </c>
     </row>
     <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B192" t="inlineStr">
         <is>
           <t>Tenancingo</t>
@@ -2915,6 +3815,11 @@
       </c>
     </row>
     <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B193" t="inlineStr">
         <is>
           <t>Texcaltitlán</t>
@@ -2928,6 +3833,11 @@
       </c>
     </row>
     <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B194" t="inlineStr">
         <is>
           <t>Tlalmanalco</t>
@@ -2941,9 +3851,14 @@
       </c>
     </row>
     <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Tlalnepantla de Baz</t>
+          <t>Tlalnepantla De Baz</t>
         </is>
       </c>
       <c r="C195">
@@ -2954,6 +3869,11 @@
       </c>
     </row>
     <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B196" t="inlineStr">
         <is>
           <t>Tlatlaya</t>
@@ -2967,6 +3887,11 @@
       </c>
     </row>
     <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B197" t="inlineStr">
         <is>
           <t>Toluca</t>
@@ -2980,6 +3905,11 @@
       </c>
     </row>
     <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B198" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2995,7 +3925,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>GUANAJUATO</t>
+          <t>Guanajuato</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -3011,6 +3941,11 @@
       </c>
     </row>
     <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B200" t="inlineStr">
         <is>
           <t>Allende</t>
@@ -3024,9 +3959,14 @@
       </c>
     </row>
     <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Apaseo el Alto</t>
+          <t>Apaseo El Alto</t>
         </is>
       </c>
       <c r="C201">
@@ -3037,6 +3977,11 @@
       </c>
     </row>
     <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B202" t="inlineStr">
         <is>
           <t>Celaya</t>
@@ -3050,6 +3995,11 @@
       </c>
     </row>
     <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B203" t="inlineStr">
         <is>
           <t>Comonfort</t>
@@ -3063,6 +4013,11 @@
       </c>
     </row>
     <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B204" t="inlineStr">
         <is>
           <t>Doctor Mora</t>
@@ -3076,9 +4031,14 @@
       </c>
     </row>
     <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna de la Independencia Nacional</t>
+          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
         </is>
       </c>
       <c r="C205">
@@ -3089,6 +4049,11 @@
       </c>
     </row>
     <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B206" t="inlineStr">
         <is>
           <t>Guanajuato</t>
@@ -3102,6 +4067,11 @@
       </c>
     </row>
     <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B207" t="inlineStr">
         <is>
           <t>Huanímaro</t>
@@ -3115,6 +4085,11 @@
       </c>
     </row>
     <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B208" t="inlineStr">
         <is>
           <t>Irapuato</t>
@@ -3128,6 +4103,11 @@
       </c>
     </row>
     <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B209" t="inlineStr">
         <is>
           <t>Jerécuaro</t>
@@ -3141,6 +4121,11 @@
       </c>
     </row>
     <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B210" t="inlineStr">
         <is>
           <t>León</t>
@@ -3154,6 +4139,11 @@
       </c>
     </row>
     <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B211" t="inlineStr">
         <is>
           <t>Pénjamo</t>
@@ -3167,6 +4157,11 @@
       </c>
     </row>
     <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B212" t="inlineStr">
         <is>
           <t>Romita</t>
@@ -3180,6 +4175,11 @@
       </c>
     </row>
     <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B213" t="inlineStr">
         <is>
           <t>Salamanca</t>
@@ -3193,6 +4193,11 @@
       </c>
     </row>
     <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B214" t="inlineStr">
         <is>
           <t>Salvatierra</t>
@@ -3206,6 +4211,11 @@
       </c>
     </row>
     <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B215" t="inlineStr">
         <is>
           <t>San Felipe</t>
@@ -3219,9 +4229,14 @@
       </c>
     </row>
     <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>San Francisco del Rincón</t>
+          <t>San Francisco Del Rincón</t>
         </is>
       </c>
       <c r="C216">
@@ -3232,9 +4247,14 @@
       </c>
     </row>
     <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>San Luis de la Paz</t>
+          <t>San Luis De La Paz</t>
         </is>
       </c>
       <c r="C217">
@@ -3245,6 +4265,11 @@
       </c>
     </row>
     <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B218" t="inlineStr">
         <is>
           <t>Santa Catarina</t>
@@ -3258,9 +4283,14 @@
       </c>
     </row>
     <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Silao de la Victoria</t>
+          <t>Silao De La Victoria</t>
         </is>
       </c>
       <c r="C219">
@@ -3271,6 +4301,11 @@
       </c>
     </row>
     <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B220" t="inlineStr">
         <is>
           <t>Tarandacuao</t>
@@ -3284,6 +4319,11 @@
       </c>
     </row>
     <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B221" t="inlineStr">
         <is>
           <t>Tarimoro</t>
@@ -3297,6 +4337,11 @@
       </c>
     </row>
     <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B222" t="inlineStr">
         <is>
           <t>Uriangato</t>
@@ -3310,6 +4355,11 @@
       </c>
     </row>
     <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B223" t="inlineStr">
         <is>
           <t>Villagrán</t>
@@ -3323,6 +4373,11 @@
       </c>
     </row>
     <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B224" t="inlineStr">
         <is>
           <t>Yuriria</t>
@@ -3361,7 +4416,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Acapulco de Juárez</t>
+          <t>Acapulco De Juárez</t>
         </is>
       </c>
       <c r="C226">
@@ -3372,9 +4427,14 @@
       </c>
     </row>
     <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Atenango del Río</t>
+          <t>Atenango Del Río</t>
         </is>
       </c>
       <c r="C227">
@@ -3385,6 +4445,11 @@
       </c>
     </row>
     <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B228" t="inlineStr">
         <is>
           <t>Atlixtac</t>
@@ -3398,9 +4463,14 @@
       </c>
     </row>
     <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Atoyac de Álvarez</t>
+          <t>Atoyac De Álvarez</t>
         </is>
       </c>
       <c r="C229">
@@ -3411,9 +4481,14 @@
       </c>
     </row>
     <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Ayutla de los Libres</t>
+          <t>Ayutla De Los Libres</t>
         </is>
       </c>
       <c r="C230">
@@ -3424,6 +4499,11 @@
       </c>
     </row>
     <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B231" t="inlineStr">
         <is>
           <t>Benito Juárez</t>
@@ -3437,9 +4517,14 @@
       </c>
     </row>
     <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Chilapa de Álvarez</t>
+          <t>Chilapa De Álvarez</t>
         </is>
       </c>
       <c r="C232">
@@ -3450,9 +4535,14 @@
       </c>
     </row>
     <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Chilpancingo de los Bravo</t>
+          <t>Chilpancingo De Los Bravo</t>
         </is>
       </c>
       <c r="C233">
@@ -3463,6 +4553,11 @@
       </c>
     </row>
     <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B234" t="inlineStr">
         <is>
           <t>Cocula</t>
@@ -3476,9 +4571,14 @@
       </c>
     </row>
     <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Coyuca de Benítez</t>
+          <t>Coyuca De Benítez</t>
         </is>
       </c>
       <c r="C235">
@@ -3489,6 +4589,11 @@
       </c>
     </row>
     <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B236" t="inlineStr">
         <is>
           <t>Cuajinicuilapa</t>
@@ -3502,9 +4607,14 @@
       </c>
     </row>
     <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Cutzamala de Pinzón</t>
+          <t>Cutzamala De Pinzón</t>
         </is>
       </c>
       <c r="C237">
@@ -3515,6 +4625,11 @@
       </c>
     </row>
     <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B238" t="inlineStr">
         <is>
           <t>Eduardo Neri</t>
@@ -3528,6 +4643,11 @@
       </c>
     </row>
     <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B239" t="inlineStr">
         <is>
           <t>General Canuto A. Neri</t>
@@ -3541,6 +4661,11 @@
       </c>
     </row>
     <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B240" t="inlineStr">
         <is>
           <t>General Heliodoro Castillo</t>
@@ -3554,9 +4679,14 @@
       </c>
     </row>
     <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Huitzuco de los Figueroa</t>
+          <t>Huitzuco De Los Figueroa</t>
         </is>
       </c>
       <c r="C241">
@@ -3567,6 +4697,11 @@
       </c>
     </row>
     <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B242" t="inlineStr">
         <is>
           <t>Juan R. Escudero</t>
@@ -3580,6 +4715,11 @@
       </c>
     </row>
     <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B243" t="inlineStr">
         <is>
           <t>Leonardo Bravo</t>
@@ -3593,6 +4733,11 @@
       </c>
     </row>
     <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B244" t="inlineStr">
         <is>
           <t>Mochitlán</t>
@@ -3606,6 +4751,11 @@
       </c>
     </row>
     <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B245" t="inlineStr">
         <is>
           <t>Ometepec</t>
@@ -3619,6 +4769,11 @@
       </c>
     </row>
     <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B246" t="inlineStr">
         <is>
           <t>Quechultenango</t>
@@ -3632,6 +4787,11 @@
       </c>
     </row>
     <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B247" t="inlineStr">
         <is>
           <t>San Marcos</t>
@@ -3645,6 +4805,11 @@
       </c>
     </row>
     <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B248" t="inlineStr">
         <is>
           <t>Tecoanapa</t>
@@ -3658,9 +4823,14 @@
       </c>
     </row>
     <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Técpan de Galeana</t>
+          <t>Técpan De Galeana</t>
         </is>
       </c>
       <c r="C249">
@@ -3671,6 +4841,11 @@
       </c>
     </row>
     <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B250" t="inlineStr">
         <is>
           <t>Teloloapan</t>
@@ -3684,9 +4859,14 @@
       </c>
     </row>
     <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Tixtla de Guerero</t>
+          <t>Tixtla De Guerero</t>
         </is>
       </c>
       <c r="C251">
@@ -3697,9 +4877,14 @@
       </c>
     </row>
     <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Tlalixtaquilla de Maldonado</t>
+          <t>Tlalixtaquilla De Maldonado</t>
         </is>
       </c>
       <c r="C252">
@@ -3710,6 +4895,11 @@
       </c>
     </row>
     <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B253" t="inlineStr">
         <is>
           <t>Tlapehuala</t>
@@ -3723,6 +4913,11 @@
       </c>
     </row>
     <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B254" t="inlineStr">
         <is>
           <t>Xochihuehuetlán</t>
@@ -3736,6 +4931,11 @@
       </c>
     </row>
     <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B255" t="inlineStr">
         <is>
           <t>Zirándaro</t>
@@ -3749,6 +4949,11 @@
       </c>
     </row>
     <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Guerero</t>
+        </is>
+      </c>
       <c r="B256" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3780,6 +4985,11 @@
       </c>
     </row>
     <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B258" t="inlineStr">
         <is>
           <t>Ajacuba</t>
@@ -3793,6 +5003,11 @@
       </c>
     </row>
     <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B259" t="inlineStr">
         <is>
           <t>Atitalaquia</t>
@@ -3806,6 +5021,11 @@
       </c>
     </row>
     <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B260" t="inlineStr">
         <is>
           <t>Atlapexco</t>
@@ -3819,6 +5039,11 @@
       </c>
     </row>
     <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B261" t="inlineStr">
         <is>
           <t>Ixmiquilpan</t>
@@ -3832,6 +5057,11 @@
       </c>
     </row>
     <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B262" t="inlineStr">
         <is>
           <t>Nicolás Flores</t>
@@ -3845,9 +5075,14 @@
       </c>
     </row>
     <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Pachuca de Soto</t>
+          <t>Pachuca De Soto</t>
         </is>
       </c>
       <c r="C263">
@@ -3858,9 +5093,14 @@
       </c>
     </row>
     <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Progreso de Obregón</t>
+          <t>Progreso De Obregón</t>
         </is>
       </c>
       <c r="C264">
@@ -3871,6 +5111,11 @@
       </c>
     </row>
     <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B265" t="inlineStr">
         <is>
           <t>Tizayuca</t>
@@ -3884,9 +5129,14 @@
       </c>
     </row>
     <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Tula de Allende</t>
+          <t>Tula De Allende</t>
         </is>
       </c>
       <c r="C266">
@@ -3897,9 +5147,14 @@
       </c>
     </row>
     <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Tulancingo de Bravo</t>
+          <t>Tulancingo De Bravo</t>
         </is>
       </c>
       <c r="C267">
@@ -3910,6 +5165,11 @@
       </c>
     </row>
     <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B268" t="inlineStr">
         <is>
           <t>Zimapán</t>
@@ -3923,6 +5183,11 @@
       </c>
     </row>
     <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B269" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3943,7 +5208,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Ahualulco de Mercado</t>
+          <t>Ahualulco De Mercado</t>
         </is>
       </c>
       <c r="C270">
@@ -3954,6 +5219,11 @@
       </c>
     </row>
     <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B271" t="inlineStr">
         <is>
           <t>Ameca</t>
@@ -3967,6 +5237,11 @@
       </c>
     </row>
     <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B272" t="inlineStr">
         <is>
           <t>Arandas</t>
@@ -3980,6 +5255,11 @@
       </c>
     </row>
     <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B273" t="inlineStr">
         <is>
           <t>Atengo</t>
@@ -3993,9 +5273,14 @@
       </c>
     </row>
     <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Autlán de Navarro</t>
+          <t>Autlán De Navarro</t>
         </is>
       </c>
       <c r="C274">
@@ -4006,6 +5291,11 @@
       </c>
     </row>
     <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B275" t="inlineStr">
         <is>
           <t>Bolaños</t>
@@ -4019,6 +5309,11 @@
       </c>
     </row>
     <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B276" t="inlineStr">
         <is>
           <t>Casimiro Castillo</t>
@@ -4032,6 +5327,11 @@
       </c>
     </row>
     <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B277" t="inlineStr">
         <is>
           <t>Chapala</t>
@@ -4045,6 +5345,11 @@
       </c>
     </row>
     <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B278" t="inlineStr">
         <is>
           <t>Cihuatlán</t>
@@ -4058,6 +5363,11 @@
       </c>
     </row>
     <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B279" t="inlineStr">
         <is>
           <t>Colotlán</t>
@@ -4071,6 +5381,11 @@
       </c>
     </row>
     <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B280" t="inlineStr">
         <is>
           <t>El Grullo</t>
@@ -4084,9 +5399,14 @@
       </c>
     </row>
     <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Encarnación de Díaz</t>
+          <t>Encarnación De Díaz</t>
         </is>
       </c>
       <c r="C281">
@@ -4097,6 +5417,11 @@
       </c>
     </row>
     <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B282" t="inlineStr">
         <is>
           <t>Etzatlán</t>
@@ -4110,6 +5435,11 @@
       </c>
     </row>
     <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B283" t="inlineStr">
         <is>
           <t>Guadalajara</t>
@@ -4123,6 +5453,11 @@
       </c>
     </row>
     <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B284" t="inlineStr">
         <is>
           <t>Huejúcar</t>
@@ -4136,9 +5471,14 @@
       </c>
     </row>
     <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Huejuquilla el Alto</t>
+          <t>Huejuquilla El Alto</t>
         </is>
       </c>
       <c r="C285">
@@ -4149,9 +5489,14 @@
       </c>
     </row>
     <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Ixtlahuacán del Río</t>
+          <t>Ixtlahuacán Del Río</t>
         </is>
       </c>
       <c r="C286">
@@ -4162,6 +5507,11 @@
       </c>
     </row>
     <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B287" t="inlineStr">
         <is>
           <t>Jalostotitlán</t>
@@ -4175,6 +5525,11 @@
       </c>
     </row>
     <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B288" t="inlineStr">
         <is>
           <t>Jamay</t>
@@ -4188,6 +5543,11 @@
       </c>
     </row>
     <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B289" t="inlineStr">
         <is>
           <t>La Barca</t>
@@ -4201,9 +5561,14 @@
       </c>
     </row>
     <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Lagos de Moreno</t>
+          <t>Lagos De Moreno</t>
         </is>
       </c>
       <c r="C290">
@@ -4214,6 +5579,11 @@
       </c>
     </row>
     <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B291" t="inlineStr">
         <is>
           <t>Mezquitic</t>
@@ -4227,6 +5597,11 @@
       </c>
     </row>
     <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B292" t="inlineStr">
         <is>
           <t>Ocotlán</t>
@@ -4240,9 +5615,14 @@
       </c>
     </row>
     <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Ojuelos de Jalisco</t>
+          <t>Ojuelos De Jalisco</t>
         </is>
       </c>
       <c r="C293">
@@ -4253,9 +5633,14 @@
       </c>
     </row>
     <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>San Cristóbal de la Barranca</t>
+          <t>San Cristóbal De La Barranca</t>
         </is>
       </c>
       <c r="C294">
@@ -4266,6 +5651,11 @@
       </c>
     </row>
     <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B295" t="inlineStr">
         <is>
           <t>San Gabriel</t>
@@ -4279,9 +5669,14 @@
       </c>
     </row>
     <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>San Juan de los Lagos</t>
+          <t>San Juan De Los Lagos</t>
         </is>
       </c>
       <c r="C296">
@@ -4292,9 +5687,14 @@
       </c>
     </row>
     <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>San Juanito de Escobedo</t>
+          <t>San Juanito De Escobedo</t>
         </is>
       </c>
       <c r="C297">
@@ -4305,6 +5705,11 @@
       </c>
     </row>
     <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B298" t="inlineStr">
         <is>
           <t>Tala</t>
@@ -4318,9 +5723,14 @@
       </c>
     </row>
     <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Tamazula de Gordiano</t>
+          <t>Tamazula De Gordiano</t>
         </is>
       </c>
       <c r="C299">
@@ -4331,6 +5741,11 @@
       </c>
     </row>
     <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B300" t="inlineStr">
         <is>
           <t>Tecalitlán</t>
@@ -4344,6 +5759,11 @@
       </c>
     </row>
     <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B301" t="inlineStr">
         <is>
           <t>Teocaltiche</t>
@@ -4357,9 +5777,14 @@
       </c>
     </row>
     <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Teocuitatlán de Corona</t>
+          <t>Teocuitatlán De Corona</t>
         </is>
       </c>
       <c r="C302">
@@ -4370,9 +5795,14 @@
       </c>
     </row>
     <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Tepatitlán de Morelos</t>
+          <t>Tepatitlán De Morelos</t>
         </is>
       </c>
       <c r="C303">
@@ -4383,6 +5813,11 @@
       </c>
     </row>
     <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B304" t="inlineStr">
         <is>
           <t>Tequila</t>
@@ -4396,9 +5831,14 @@
       </c>
     </row>
     <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Tizapán el Alto</t>
+          <t>Tizapán El Alto</t>
         </is>
       </c>
       <c r="C305">
@@ -4409,6 +5849,11 @@
       </c>
     </row>
     <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B306" t="inlineStr">
         <is>
           <t>Tomatlán</t>
@@ -4422,6 +5867,11 @@
       </c>
     </row>
     <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B307" t="inlineStr">
         <is>
           <t>Tototlán</t>
@@ -4435,6 +5885,11 @@
       </c>
     </row>
     <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B308" t="inlineStr">
         <is>
           <t>Villa Guerero</t>
@@ -4448,9 +5903,14 @@
       </c>
     </row>
     <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Yahualica de González Gallo</t>
+          <t>Yahualica De González Gallo</t>
         </is>
       </c>
       <c r="C309">
@@ -4461,6 +5921,11 @@
       </c>
     </row>
     <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B310" t="inlineStr">
         <is>
           <t>Zapotlanejo</t>
@@ -4474,6 +5939,11 @@
       </c>
     </row>
     <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B311" t="inlineStr">
         <is>
           <t>Total</t>
@@ -4505,6 +5975,11 @@
       </c>
     </row>
     <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B313" t="inlineStr">
         <is>
           <t>Aguililla</t>
@@ -4518,6 +5993,11 @@
       </c>
     </row>
     <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B314" t="inlineStr">
         <is>
           <t>Apatzingán</t>
@@ -4531,6 +6011,11 @@
       </c>
     </row>
     <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B315" t="inlineStr">
         <is>
           <t>Ario</t>
@@ -4544,6 +6029,11 @@
       </c>
     </row>
     <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B316" t="inlineStr">
         <is>
           <t>Buenavista</t>
@@ -4557,9 +6047,14 @@
       </c>
     </row>
     <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Cojumatlán de Régules</t>
+          <t>Cojumatlán De Régules</t>
         </is>
       </c>
       <c r="C317">
@@ -4570,6 +6065,11 @@
       </c>
     </row>
     <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B318" t="inlineStr">
         <is>
           <t>Contepec</t>
@@ -4583,6 +6083,11 @@
       </c>
     </row>
     <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B319" t="inlineStr">
         <is>
           <t>Erongarícuaro</t>
@@ -4596,6 +6101,11 @@
       </c>
     </row>
     <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B320" t="inlineStr">
         <is>
           <t>Gabriel Zamora</t>
@@ -4609,6 +6119,11 @@
       </c>
     </row>
     <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B321" t="inlineStr">
         <is>
           <t>Hidalgo</t>
@@ -4622,6 +6137,11 @@
       </c>
     </row>
     <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B322" t="inlineStr">
         <is>
           <t>Huandacareo</t>
@@ -4635,6 +6155,11 @@
       </c>
     </row>
     <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B323" t="inlineStr">
         <is>
           <t>Huetamo</t>
@@ -4648,6 +6173,11 @@
       </c>
     </row>
     <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B324" t="inlineStr">
         <is>
           <t>Jacona</t>
@@ -4661,6 +6191,11 @@
       </c>
     </row>
     <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B325" t="inlineStr">
         <is>
           <t>Jiménez</t>
@@ -4674,6 +6209,11 @@
       </c>
     </row>
     <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B326" t="inlineStr">
         <is>
           <t>Jiquilpan</t>
@@ -4687,6 +6227,11 @@
       </c>
     </row>
     <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B327" t="inlineStr">
         <is>
           <t>La Huacana</t>
@@ -4700,6 +6245,11 @@
       </c>
     </row>
     <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B328" t="inlineStr">
         <is>
           <t>La Piedad</t>
@@ -4713,6 +6263,11 @@
       </c>
     </row>
     <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B329" t="inlineStr">
         <is>
           <t>Lázaro Cárdenas</t>
@@ -4726,6 +6281,11 @@
       </c>
     </row>
     <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B330" t="inlineStr">
         <is>
           <t>Los Reyes</t>
@@ -4739,6 +6299,11 @@
       </c>
     </row>
     <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B331" t="inlineStr">
         <is>
           <t>Maravatío</t>
@@ -4752,6 +6317,11 @@
       </c>
     </row>
     <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B332" t="inlineStr">
         <is>
           <t>Morelia</t>
@@ -4765,6 +6335,11 @@
       </c>
     </row>
     <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B333" t="inlineStr">
         <is>
           <t>Morelos</t>
@@ -4778,6 +6353,11 @@
       </c>
     </row>
     <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B334" t="inlineStr">
         <is>
           <t>Múgica</t>
@@ -4791,6 +6371,11 @@
       </c>
     </row>
     <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B335" t="inlineStr">
         <is>
           <t>Nocupétaro</t>
@@ -4804,6 +6389,11 @@
       </c>
     </row>
     <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B336" t="inlineStr">
         <is>
           <t>Paracho</t>
@@ -4817,6 +6407,11 @@
       </c>
     </row>
     <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B337" t="inlineStr">
         <is>
           <t>Parácuaro</t>
@@ -4830,6 +6425,11 @@
       </c>
     </row>
     <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B338" t="inlineStr">
         <is>
           <t>Pátzcuaro</t>
@@ -4843,6 +6443,11 @@
       </c>
     </row>
     <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B339" t="inlineStr">
         <is>
           <t>Quiroga</t>
@@ -4856,6 +6461,11 @@
       </c>
     </row>
     <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B340" t="inlineStr">
         <is>
           <t>Sahuayo</t>
@@ -4869,6 +6479,11 @@
       </c>
     </row>
     <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B341" t="inlineStr">
         <is>
           <t>Tacámbaro</t>
@@ -4882,6 +6497,11 @@
       </c>
     </row>
     <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B342" t="inlineStr">
         <is>
           <t>Tanhuato</t>
@@ -4895,6 +6515,11 @@
       </c>
     </row>
     <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B343" t="inlineStr">
         <is>
           <t>Tingüindín</t>
@@ -4908,9 +6533,14 @@
       </c>
     </row>
     <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Tiquicheo de Nicolás Romero</t>
+          <t>Tiquicheo De Nicolás Romero</t>
         </is>
       </c>
       <c r="C344">
@@ -4921,6 +6551,11 @@
       </c>
     </row>
     <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B345" t="inlineStr">
         <is>
           <t>Tlalpujahua</t>
@@ -4934,6 +6569,11 @@
       </c>
     </row>
     <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B346" t="inlineStr">
         <is>
           <t>Tumbiscatío</t>
@@ -4947,6 +6587,11 @@
       </c>
     </row>
     <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B347" t="inlineStr">
         <is>
           <t>Turicato</t>
@@ -4960,6 +6605,11 @@
       </c>
     </row>
     <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B348" t="inlineStr">
         <is>
           <t>Tuxpan</t>
@@ -4973,6 +6623,11 @@
       </c>
     </row>
     <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B349" t="inlineStr">
         <is>
           <t>Tuzantla</t>
@@ -4986,6 +6641,11 @@
       </c>
     </row>
     <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B350" t="inlineStr">
         <is>
           <t>Tzintzuntzan</t>
@@ -4999,6 +6659,11 @@
       </c>
     </row>
     <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B351" t="inlineStr">
         <is>
           <t>Uruapan</t>
@@ -5012,6 +6677,11 @@
       </c>
     </row>
     <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B352" t="inlineStr">
         <is>
           <t>Yurécuaro</t>
@@ -5025,6 +6695,11 @@
       </c>
     </row>
     <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B353" t="inlineStr">
         <is>
           <t>Zamora</t>
@@ -5038,6 +6713,11 @@
       </c>
     </row>
     <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B354" t="inlineStr">
         <is>
           <t>Zinapécuaro</t>
@@ -5051,6 +6731,11 @@
       </c>
     </row>
     <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B355" t="inlineStr">
         <is>
           <t>Zitácuaro</t>
@@ -5064,6 +6749,11 @@
       </c>
     </row>
     <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B356" t="inlineStr">
         <is>
           <t>Total</t>
@@ -5095,6 +6785,11 @@
       </c>
     </row>
     <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B358" t="inlineStr">
         <is>
           <t>Cuautla</t>
@@ -5108,6 +6803,11 @@
       </c>
     </row>
     <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B359" t="inlineStr">
         <is>
           <t>Cuernavaca</t>
@@ -5121,9 +6821,14 @@
       </c>
     </row>
     <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Puente de Ixtla</t>
+          <t>Puente De Ixtla</t>
         </is>
       </c>
       <c r="C360">
@@ -5134,6 +6839,11 @@
       </c>
     </row>
     <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B361" t="inlineStr">
         <is>
           <t>Tepalcingo</t>
@@ -5147,6 +6857,11 @@
       </c>
     </row>
     <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B362" t="inlineStr">
         <is>
           <t>Tlaquiltenango</t>
@@ -5160,6 +6875,11 @@
       </c>
     </row>
     <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B363" t="inlineStr">
         <is>
           <t>Yautepec</t>
@@ -5173,6 +6893,11 @@
       </c>
     </row>
     <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B364" t="inlineStr">
         <is>
           <t>Total</t>
@@ -5204,6 +6929,11 @@
       </c>
     </row>
     <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B366" t="inlineStr">
         <is>
           <t>Compostela</t>
@@ -5217,6 +6947,11 @@
       </c>
     </row>
     <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B367" t="inlineStr">
         <is>
           <t>Del Nayar</t>
@@ -5230,6 +6965,11 @@
       </c>
     </row>
     <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B368" t="inlineStr">
         <is>
           <t>Huajicori</t>
@@ -5243,6 +6983,11 @@
       </c>
     </row>
     <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B369" t="inlineStr">
         <is>
           <t>San Blas</t>
@@ -5256,6 +7001,11 @@
       </c>
     </row>
     <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B370" t="inlineStr">
         <is>
           <t>Santiago Ixcuintla</t>
@@ -5269,6 +7019,11 @@
       </c>
     </row>
     <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B371" t="inlineStr">
         <is>
           <t>Tecuala</t>
@@ -5282,6 +7037,11 @@
       </c>
     </row>
     <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B372" t="inlineStr">
         <is>
           <t>Tepic</t>
@@ -5295,6 +7055,11 @@
       </c>
     </row>
     <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B373" t="inlineStr">
         <is>
           <t>Tuxpan</t>
@@ -5308,6 +7073,11 @@
       </c>
     </row>
     <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B374" t="inlineStr">
         <is>
           <t>Total</t>
@@ -5339,6 +7109,11 @@
       </c>
     </row>
     <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B376" t="inlineStr">
         <is>
           <t>Guadalupe</t>
@@ -5352,6 +7127,11 @@
       </c>
     </row>
     <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B377" t="inlineStr">
         <is>
           <t>Linares</t>
@@ -5365,9 +7145,14 @@
       </c>
     </row>
     <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Mier y Noriega</t>
+          <t>Mier Y Noriega</t>
         </is>
       </c>
       <c r="C378">
@@ -5378,6 +7163,11 @@
       </c>
     </row>
     <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B379" t="inlineStr">
         <is>
           <t>Monterrey</t>
@@ -5391,9 +7181,14 @@
       </c>
     </row>
     <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>San Nicolás de los Garza</t>
+          <t>San Nicolás De Los Garza</t>
         </is>
       </c>
       <c r="C380">
@@ -5404,6 +7199,11 @@
       </c>
     </row>
     <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B381" t="inlineStr">
         <is>
           <t>San Pedro Garza García</t>
@@ -5417,6 +7217,11 @@
       </c>
     </row>
     <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B382" t="inlineStr">
         <is>
           <t>Total</t>
@@ -5448,6 +7253,11 @@
       </c>
     </row>
     <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B384" t="inlineStr">
         <is>
           <t>Asunción Cuyotepeji</t>
@@ -5461,9 +7271,14 @@
       </c>
     </row>
     <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Guevea de Humboldt</t>
+          <t>Guevea De Humboldt</t>
         </is>
       </c>
       <c r="C385">
@@ -5474,9 +7289,14 @@
       </c>
     </row>
     <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Heroica Ciudad de Ejutla de Crespo</t>
+          <t>Heroica Ciudad De Ejutla De Crespo</t>
         </is>
       </c>
       <c r="C386">
@@ -5487,9 +7307,14 @@
       </c>
     </row>
     <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Heroica Ciudad de Tlaxiaco</t>
+          <t>Heroica Ciudad De Tlaxiaco</t>
         </is>
       </c>
       <c r="C387">
@@ -5500,9 +7325,14 @@
       </c>
     </row>
     <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Ixtlán de Juárez</t>
+          <t>Ixtlán De Juárez</t>
         </is>
       </c>
       <c r="C388">
@@ -5513,9 +7343,14 @@
       </c>
     </row>
     <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Heroica Ciudad de Juchitán de Zaragoza</t>
+          <t>Heroica Ciudad De Juchitán De Zaragoza</t>
         </is>
       </c>
       <c r="C389">
@@ -5526,6 +7361,11 @@
       </c>
     </row>
     <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B390" t="inlineStr">
         <is>
           <t>Loma Bonita</t>
@@ -5539,6 +7379,11 @@
       </c>
     </row>
     <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B391" t="inlineStr">
         <is>
           <t>Magdalena Tequisistlán</t>
@@ -5552,9 +7397,14 @@
       </c>
     </row>
     <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Mariscala de Juárez</t>
+          <t>Mariscala De Juárez</t>
         </is>
       </c>
       <c r="C392">
@@ -5565,9 +7415,14 @@
       </c>
     </row>
     <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Miahuatlán de Porfirio Díaz</t>
+          <t>Miahuatlán De Porfirio Díaz</t>
         </is>
       </c>
       <c r="C393">
@@ -5578,9 +7433,14 @@
       </c>
     </row>
     <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Oaxaca de Juárez</t>
+          <t>Oaxaca De Juárez</t>
         </is>
       </c>
       <c r="C394">
@@ -5591,6 +7451,11 @@
       </c>
     </row>
     <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B395" t="inlineStr">
         <is>
           <t>San Dionisio Ocotepec</t>
@@ -5604,6 +7469,11 @@
       </c>
     </row>
     <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B396" t="inlineStr">
         <is>
           <t>San Juan Bautista Tlachichilco</t>
@@ -5617,6 +7487,11 @@
       </c>
     </row>
     <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B397" t="inlineStr">
         <is>
           <t>San Juan Bautista Tuxtepec</t>
@@ -5630,6 +7505,11 @@
       </c>
     </row>
     <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B398" t="inlineStr">
         <is>
           <t>San Juan Guichicovi</t>
@@ -5643,6 +7523,11 @@
       </c>
     </row>
     <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B399" t="inlineStr">
         <is>
           <t>San Lorenzo Victoria</t>
@@ -5656,6 +7541,11 @@
       </c>
     </row>
     <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B400" t="inlineStr">
         <is>
           <t>San Pedro Tapanatepec</t>
@@ -5669,6 +7559,11 @@
       </c>
     </row>
     <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B401" t="inlineStr">
         <is>
           <t>Santa María Guienagati</t>
@@ -5682,6 +7577,11 @@
       </c>
     </row>
     <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B402" t="inlineStr">
         <is>
           <t>Santa María Huatulco</t>
@@ -5695,6 +7595,11 @@
       </c>
     </row>
     <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B403" t="inlineStr">
         <is>
           <t>Santa María Jacatepec</t>
@@ -5708,6 +7613,11 @@
       </c>
     </row>
     <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B404" t="inlineStr">
         <is>
           <t>Santa María Jaltianguis</t>
@@ -5721,6 +7631,11 @@
       </c>
     </row>
     <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B405" t="inlineStr">
         <is>
           <t>Santiago Juxtlahuaca</t>
@@ -5734,6 +7649,11 @@
       </c>
     </row>
     <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B406" t="inlineStr">
         <is>
           <t>Santiago Yosondúa</t>
@@ -5747,6 +7667,11 @@
       </c>
     </row>
     <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B407" t="inlineStr">
         <is>
           <t>Santo Domingo Armenta</t>
@@ -5760,6 +7685,11 @@
       </c>
     </row>
     <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B408" t="inlineStr">
         <is>
           <t>Santo Domingo Tehuantepec</t>
@@ -5773,6 +7703,11 @@
       </c>
     </row>
     <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B409" t="inlineStr">
         <is>
           <t>Silacayoápam</t>
@@ -5786,9 +7721,14 @@
       </c>
     </row>
     <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Teotitlán del Valle</t>
+          <t>Teotitlán Del Valle</t>
         </is>
       </c>
       <c r="C410">
@@ -5799,9 +7739,14 @@
       </c>
     </row>
     <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Tepelmeme Villa de Morelos</t>
+          <t>Tepelmeme Villa De Morelos</t>
         </is>
       </c>
       <c r="C411">
@@ -5812,9 +7757,14 @@
       </c>
     </row>
     <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Villa Sola de Vega</t>
+          <t>Villa Sola De Vega</t>
         </is>
       </c>
       <c r="C412">
@@ -5825,6 +7775,11 @@
       </c>
     </row>
     <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B413" t="inlineStr">
         <is>
           <t>Total</t>
@@ -5856,6 +7811,11 @@
       </c>
     </row>
     <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B415" t="inlineStr">
         <is>
           <t>Atzitzihuacán</t>
@@ -5869,6 +7829,11 @@
       </c>
     </row>
     <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B416" t="inlineStr">
         <is>
           <t>Caltepec</t>
@@ -5882,6 +7847,11 @@
       </c>
     </row>
     <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B417" t="inlineStr">
         <is>
           <t>Cañada Morelos</t>
@@ -5895,6 +7865,11 @@
       </c>
     </row>
     <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B418" t="inlineStr">
         <is>
           <t>Chichiquila</t>
@@ -5908,6 +7883,11 @@
       </c>
     </row>
     <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B419" t="inlineStr">
         <is>
           <t>Chietla</t>
@@ -5921,6 +7901,11 @@
       </c>
     </row>
     <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B420" t="inlineStr">
         <is>
           <t>Coatepec</t>
@@ -5934,6 +7919,11 @@
       </c>
     </row>
     <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B421" t="inlineStr">
         <is>
           <t>Coronango</t>
@@ -5947,6 +7937,11 @@
       </c>
     </row>
     <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B422" t="inlineStr">
         <is>
           <t>Esperanza</t>
@@ -5960,6 +7955,11 @@
       </c>
     </row>
     <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B423" t="inlineStr">
         <is>
           <t>Huehuetla</t>
@@ -5973,6 +7973,11 @@
       </c>
     </row>
     <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B424" t="inlineStr">
         <is>
           <t>Huitziltepec</t>
@@ -5986,6 +7991,11 @@
       </c>
     </row>
     <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B425" t="inlineStr">
         <is>
           <t>Ixcaquixtla</t>
@@ -5999,9 +8009,14 @@
       </c>
     </row>
     <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Los Reyes de Juárez</t>
+          <t>Los Reyes De Juárez</t>
         </is>
       </c>
       <c r="C426">
@@ -6012,9 +8027,14 @@
       </c>
     </row>
     <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Palmar de Bravo</t>
+          <t>Palmar De Bravo</t>
         </is>
       </c>
       <c r="C427">
@@ -6025,6 +8045,11 @@
       </c>
     </row>
     <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B428" t="inlineStr">
         <is>
           <t>Puebla</t>
@@ -6038,6 +8063,11 @@
       </c>
     </row>
     <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B429" t="inlineStr">
         <is>
           <t>Quecholac</t>
@@ -6051,6 +8081,11 @@
       </c>
     </row>
     <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B430" t="inlineStr">
         <is>
           <t>San Martín Texmelucan</t>
@@ -6064,6 +8099,11 @@
       </c>
     </row>
     <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B431" t="inlineStr">
         <is>
           <t>San Matías Tlalancaleca</t>
@@ -6077,9 +8117,14 @@
       </c>
     </row>
     <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>San Salvador el Seco</t>
+          <t>San Salvador El Seco</t>
         </is>
       </c>
       <c r="C432">
@@ -6090,6 +8135,11 @@
       </c>
     </row>
     <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B433" t="inlineStr">
         <is>
           <t>Santiago Miahuatlán</t>
@@ -6103,6 +8153,11 @@
       </c>
     </row>
     <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B434" t="inlineStr">
         <is>
           <t>Tecamachalco</t>
@@ -6116,6 +8171,11 @@
       </c>
     </row>
     <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B435" t="inlineStr">
         <is>
           <t>Tehuacán</t>
@@ -6129,9 +8189,14 @@
       </c>
     </row>
     <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Tepexi de Rodríguez</t>
+          <t>Tepexi De Rodríguez</t>
         </is>
       </c>
       <c r="C436">
@@ -6142,9 +8207,14 @@
       </c>
     </row>
     <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Tetela de Ocampo</t>
+          <t>Tetela De Ocampo</t>
         </is>
       </c>
       <c r="C437">
@@ -6155,9 +8225,14 @@
       </c>
     </row>
     <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Tlacotepec de Benito Juárez</t>
+          <t>Tlacotepec De Benito Juárez</t>
         </is>
       </c>
       <c r="C438">
@@ -6168,6 +8243,11 @@
       </c>
     </row>
     <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B439" t="inlineStr">
         <is>
           <t>Tlatlauquitepec</t>
@@ -6181,6 +8261,11 @@
       </c>
     </row>
     <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B440" t="inlineStr">
         <is>
           <t>Tochtepec</t>
@@ -6194,6 +8279,11 @@
       </c>
     </row>
     <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B441" t="inlineStr">
         <is>
           <t>Yehualtepec</t>
@@ -6207,6 +8297,11 @@
       </c>
     </row>
     <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B442" t="inlineStr">
         <is>
           <t>Zacapala</t>
@@ -6220,6 +8315,11 @@
       </c>
     </row>
     <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B443" t="inlineStr">
         <is>
           <t>Zacatlán</t>
@@ -6233,6 +8333,11 @@
       </c>
     </row>
     <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B444" t="inlineStr">
         <is>
           <t>Total</t>
@@ -6253,7 +8358,7 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>Amealco de Bonfil</t>
+          <t>Amealco De Bonfil</t>
         </is>
       </c>
       <c r="C445">
@@ -6264,9 +8369,14 @@
       </c>
     </row>
     <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Cadereyta de Montes</t>
+          <t>Cadereyta De Montes</t>
         </is>
       </c>
       <c r="C446">
@@ -6277,9 +8387,14 @@
       </c>
     </row>
     <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Jalpan de Serra</t>
+          <t>Jalpan De Serra</t>
         </is>
       </c>
       <c r="C447">
@@ -6290,9 +8405,14 @@
       </c>
     </row>
     <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Landa de Matamoros</t>
+          <t>Landa De Matamoros</t>
         </is>
       </c>
       <c r="C448">
@@ -6303,6 +8423,11 @@
       </c>
     </row>
     <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B449" t="inlineStr">
         <is>
           <t>Querétaro</t>
@@ -6316,6 +8441,11 @@
       </c>
     </row>
     <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B450" t="inlineStr">
         <is>
           <t>Total</t>
@@ -6347,6 +8477,11 @@
       </c>
     </row>
     <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>Quintana Roo</t>
+        </is>
+      </c>
       <c r="B452" t="inlineStr">
         <is>
           <t>Othón P. Blanco</t>
@@ -6360,6 +8495,11 @@
       </c>
     </row>
     <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>Quintana Roo</t>
+        </is>
+      </c>
       <c r="B453" t="inlineStr">
         <is>
           <t>Total</t>
@@ -6391,6 +8531,11 @@
       </c>
     </row>
     <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B455" t="inlineStr">
         <is>
           <t>Alaquines</t>
@@ -6404,6 +8549,11 @@
       </c>
     </row>
     <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B456" t="inlineStr">
         <is>
           <t>Aquismón</t>
@@ -6417,6 +8567,11 @@
       </c>
     </row>
     <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B457" t="inlineStr">
         <is>
           <t>Cárdenas</t>
@@ -6430,6 +8585,11 @@
       </c>
     </row>
     <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B458" t="inlineStr">
         <is>
           <t>Cerritos</t>
@@ -6443,9 +8603,14 @@
       </c>
     </row>
     <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Ciudad del Maíz</t>
+          <t>Ciudad Del Maíz</t>
         </is>
       </c>
       <c r="C459">
@@ -6456,6 +8621,11 @@
       </c>
     </row>
     <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B460" t="inlineStr">
         <is>
           <t>Ciudad Fernández</t>
@@ -6469,6 +8639,11 @@
       </c>
     </row>
     <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B461" t="inlineStr">
         <is>
           <t>Ciudad Valles</t>
@@ -6482,6 +8657,11 @@
       </c>
     </row>
     <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B462" t="inlineStr">
         <is>
           <t>Moctezuma</t>
@@ -6495,6 +8675,11 @@
       </c>
     </row>
     <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B463" t="inlineStr">
         <is>
           <t>Rioverde</t>
@@ -6508,9 +8693,14 @@
       </c>
     </row>
     <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>San Ciro de Acosta</t>
+          <t>San Ciro De Acosta</t>
         </is>
       </c>
       <c r="C464">
@@ -6521,6 +8711,11 @@
       </c>
     </row>
     <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B465" t="inlineStr">
         <is>
           <t>San Luis Potosí</t>
@@ -6534,9 +8729,14 @@
       </c>
     </row>
     <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>Santa María del Río</t>
+          <t>Santa María Del Río</t>
         </is>
       </c>
       <c r="C466">
@@ -6547,6 +8747,11 @@
       </c>
     </row>
     <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B467" t="inlineStr">
         <is>
           <t>Santo Domingo</t>
@@ -6560,9 +8765,14 @@
       </c>
     </row>
     <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>Villa de Ramos</t>
+          <t>Villa De Ramos</t>
         </is>
       </c>
       <c r="C468">
@@ -6573,6 +8783,11 @@
       </c>
     </row>
     <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B469" t="inlineStr">
         <is>
           <t>Villa Juárez</t>
@@ -6586,6 +8801,11 @@
       </c>
     </row>
     <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B470" t="inlineStr">
         <is>
           <t>Zaragoza</t>
@@ -6599,6 +8819,11 @@
       </c>
     </row>
     <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B471" t="inlineStr">
         <is>
           <t>Total</t>
@@ -6630,6 +8855,11 @@
       </c>
     </row>
     <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B473" t="inlineStr">
         <is>
           <t>Badiraguato</t>
@@ -6643,6 +8873,11 @@
       </c>
     </row>
     <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B474" t="inlineStr">
         <is>
           <t>Choix</t>
@@ -6656,6 +8891,11 @@
       </c>
     </row>
     <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B475" t="inlineStr">
         <is>
           <t>Concordia</t>
@@ -6669,6 +8909,11 @@
       </c>
     </row>
     <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B476" t="inlineStr">
         <is>
           <t>Culiacán</t>
@@ -6682,6 +8927,11 @@
       </c>
     </row>
     <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B477" t="inlineStr">
         <is>
           <t>El Fuerte</t>
@@ -6695,6 +8945,11 @@
       </c>
     </row>
     <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B478" t="inlineStr">
         <is>
           <t>Guasave</t>
@@ -6708,6 +8963,11 @@
       </c>
     </row>
     <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B479" t="inlineStr">
         <is>
           <t>Mazatlán</t>
@@ -6721,6 +8981,11 @@
       </c>
     </row>
     <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B480" t="inlineStr">
         <is>
           <t>Mocorito</t>
@@ -6734,6 +8999,11 @@
       </c>
     </row>
     <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B481" t="inlineStr">
         <is>
           <t>Navolato</t>
@@ -6747,6 +9017,11 @@
       </c>
     </row>
     <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B482" t="inlineStr">
         <is>
           <t>Rosario</t>
@@ -6760,6 +9035,11 @@
       </c>
     </row>
     <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B483" t="inlineStr">
         <is>
           <t>Salvador Alvarado</t>
@@ -6773,6 +9053,11 @@
       </c>
     </row>
     <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B484" t="inlineStr">
         <is>
           <t>San Ignacio</t>
@@ -6786,6 +9071,11 @@
       </c>
     </row>
     <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B485" t="inlineStr">
         <is>
           <t>Sinaloa</t>
@@ -6799,6 +9089,11 @@
       </c>
     </row>
     <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B486" t="inlineStr">
         <is>
           <t>Total</t>
@@ -6830,6 +9125,11 @@
       </c>
     </row>
     <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B488" t="inlineStr">
         <is>
           <t>Alamos</t>
@@ -6843,6 +9143,11 @@
       </c>
     </row>
     <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B489" t="inlineStr">
         <is>
           <t>Altar</t>
@@ -6856,6 +9161,11 @@
       </c>
     </row>
     <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B490" t="inlineStr">
         <is>
           <t>Arizpe</t>
@@ -6869,6 +9179,11 @@
       </c>
     </row>
     <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B491" t="inlineStr">
         <is>
           <t>Bacanora</t>
@@ -6882,6 +9197,11 @@
       </c>
     </row>
     <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B492" t="inlineStr">
         <is>
           <t>Bácum</t>
@@ -6895,6 +9215,11 @@
       </c>
     </row>
     <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B493" t="inlineStr">
         <is>
           <t>Caborca</t>
@@ -6908,6 +9233,11 @@
       </c>
     </row>
     <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B494" t="inlineStr">
         <is>
           <t>Cajeme</t>
@@ -6921,6 +9251,11 @@
       </c>
     </row>
     <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B495" t="inlineStr">
         <is>
           <t>Cananea</t>
@@ -6934,6 +9269,11 @@
       </c>
     </row>
     <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B496" t="inlineStr">
         <is>
           <t>Cumpas</t>
@@ -6947,6 +9287,11 @@
       </c>
     </row>
     <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B497" t="inlineStr">
         <is>
           <t>Guaymas</t>
@@ -6960,6 +9305,11 @@
       </c>
     </row>
     <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B498" t="inlineStr">
         <is>
           <t>Hermosillo</t>
@@ -6973,6 +9323,11 @@
       </c>
     </row>
     <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B499" t="inlineStr">
         <is>
           <t>Naco</t>
@@ -6986,9 +9341,14 @@
       </c>
     </row>
     <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Nacozari de García</t>
+          <t>Nacozari De García</t>
         </is>
       </c>
       <c r="C500">
@@ -6999,6 +9359,11 @@
       </c>
     </row>
     <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B501" t="inlineStr">
         <is>
           <t>Nogales</t>
@@ -7012,6 +9377,11 @@
       </c>
     </row>
     <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B502" t="inlineStr">
         <is>
           <t>Puerto Peñasco</t>
@@ -7025,6 +9395,11 @@
       </c>
     </row>
     <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B503" t="inlineStr">
         <is>
           <t>San Luis Río Colorado</t>
@@ -7038,6 +9413,11 @@
       </c>
     </row>
     <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B504" t="inlineStr">
         <is>
           <t>Total</t>
@@ -7069,6 +9449,11 @@
       </c>
     </row>
     <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B506" t="inlineStr">
         <is>
           <t>Huimanguillo</t>
@@ -7082,6 +9467,11 @@
       </c>
     </row>
     <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B507" t="inlineStr">
         <is>
           <t>Teapa</t>
@@ -7095,6 +9485,11 @@
       </c>
     </row>
     <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B508" t="inlineStr">
         <is>
           <t>Total</t>
@@ -7126,6 +9521,11 @@
       </c>
     </row>
     <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B510" t="inlineStr">
         <is>
           <t>El Mante</t>
@@ -7139,6 +9539,11 @@
       </c>
     </row>
     <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B511" t="inlineStr">
         <is>
           <t>González</t>
@@ -7152,6 +9557,11 @@
       </c>
     </row>
     <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B512" t="inlineStr">
         <is>
           <t>Hidalgo</t>
@@ -7165,6 +9575,11 @@
       </c>
     </row>
     <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B513" t="inlineStr">
         <is>
           <t>Matamoros</t>
@@ -7178,6 +9593,11 @@
       </c>
     </row>
     <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B514" t="inlineStr">
         <is>
           <t>Reynosa</t>
@@ -7191,6 +9611,11 @@
       </c>
     </row>
     <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B515" t="inlineStr">
         <is>
           <t>Río Bravo</t>
@@ -7204,6 +9629,11 @@
       </c>
     </row>
     <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B516" t="inlineStr">
         <is>
           <t>Tampico</t>
@@ -7217,6 +9647,11 @@
       </c>
     </row>
     <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B517" t="inlineStr">
         <is>
           <t>Victoria</t>
@@ -7230,6 +9665,11 @@
       </c>
     </row>
     <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B518" t="inlineStr">
         <is>
           <t>Total</t>
@@ -7261,6 +9701,11 @@
       </c>
     </row>
     <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B520" t="inlineStr">
         <is>
           <t>Calpulalpan</t>
@@ -7274,6 +9719,11 @@
       </c>
     </row>
     <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B521" t="inlineStr">
         <is>
           <t>Chiautempan</t>
@@ -7287,9 +9737,14 @@
       </c>
     </row>
     <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>Nanacamilpa de Mariano Arista</t>
+          <t>Nanacamilpa De Mariano Arista</t>
         </is>
       </c>
       <c r="C522">
@@ -7300,6 +9755,11 @@
       </c>
     </row>
     <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B523" t="inlineStr">
         <is>
           <t>Natívitas</t>
@@ -7313,6 +9773,11 @@
       </c>
     </row>
     <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B524" t="inlineStr">
         <is>
           <t>Xaltocan</t>
@@ -7326,6 +9791,11 @@
       </c>
     </row>
     <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B525" t="inlineStr">
         <is>
           <t>Total</t>
@@ -7357,6 +9827,11 @@
       </c>
     </row>
     <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B527" t="inlineStr">
         <is>
           <t>Alvarado</t>
@@ -7370,6 +9845,11 @@
       </c>
     </row>
     <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B528" t="inlineStr">
         <is>
           <t>Catemaco</t>
@@ -7383,6 +9863,11 @@
       </c>
     </row>
     <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B529" t="inlineStr">
         <is>
           <t>Cerro Azul</t>
@@ -7396,6 +9881,11 @@
       </c>
     </row>
     <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B530" t="inlineStr">
         <is>
           <t>Chacaltianguis</t>
@@ -7409,6 +9899,11 @@
       </c>
     </row>
     <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B531" t="inlineStr">
         <is>
           <t>Coatzacoalcos</t>
@@ -7422,6 +9917,11 @@
       </c>
     </row>
     <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B532" t="inlineStr">
         <is>
           <t>Córdoba</t>
@@ -7435,9 +9935,14 @@
       </c>
     </row>
     <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>Cosamaloapan de Carpio</t>
+          <t>Cosamaloapan De Carpio</t>
         </is>
       </c>
       <c r="C533">
@@ -7448,6 +9953,11 @@
       </c>
     </row>
     <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B534" t="inlineStr">
         <is>
           <t>Coscomatepec</t>
@@ -7461,6 +9971,11 @@
       </c>
     </row>
     <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B535" t="inlineStr">
         <is>
           <t>Cosoleacaque</t>
@@ -7474,6 +9989,11 @@
       </c>
     </row>
     <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B536" t="inlineStr">
         <is>
           <t>Huatusco</t>
@@ -7487,9 +10007,14 @@
       </c>
     </row>
     <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>Ignacio de la Llave</t>
+          <t>Ignacio De La Llave</t>
         </is>
       </c>
       <c r="C537">
@@ -7500,6 +10025,11 @@
       </c>
     </row>
     <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B538" t="inlineStr">
         <is>
           <t>Isla</t>
@@ -7513,9 +10043,14 @@
       </c>
     </row>
     <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>Martínez de la Torre</t>
+          <t>Martínez De La Torre</t>
         </is>
       </c>
       <c r="C539">
@@ -7526,6 +10061,11 @@
       </c>
     </row>
     <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B540" t="inlineStr">
         <is>
           <t>Minatitlán</t>
@@ -7539,6 +10079,11 @@
       </c>
     </row>
     <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B541" t="inlineStr">
         <is>
           <t>Misantla</t>
@@ -7552,6 +10097,11 @@
       </c>
     </row>
     <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B542" t="inlineStr">
         <is>
           <t>Pajapan</t>
@@ -7565,6 +10115,11 @@
       </c>
     </row>
     <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B543" t="inlineStr">
         <is>
           <t>Pánuco</t>
@@ -7578,6 +10133,11 @@
       </c>
     </row>
     <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B544" t="inlineStr">
         <is>
           <t>Playa Vicente</t>
@@ -7591,6 +10151,11 @@
       </c>
     </row>
     <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B545" t="inlineStr">
         <is>
           <t>San Andrés Tuxtla</t>
@@ -7604,9 +10169,14 @@
       </c>
     </row>
     <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>Sayula de Alemán</t>
+          <t>Sayula De Alemán</t>
         </is>
       </c>
       <c r="C546">
@@ -7617,6 +10187,11 @@
       </c>
     </row>
     <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B547" t="inlineStr">
         <is>
           <t>Sochiapa</t>
@@ -7630,6 +10205,11 @@
       </c>
     </row>
     <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B548" t="inlineStr">
         <is>
           <t>Tepetzintla</t>
@@ -7643,6 +10223,11 @@
       </c>
     </row>
     <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B549" t="inlineStr">
         <is>
           <t>Tezonapa</t>
@@ -7656,6 +10241,11 @@
       </c>
     </row>
     <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B550" t="inlineStr">
         <is>
           <t>Tlacojalpan</t>
@@ -7669,6 +10259,11 @@
       </c>
     </row>
     <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B551" t="inlineStr">
         <is>
           <t>Totutla</t>
@@ -7682,6 +10277,11 @@
       </c>
     </row>
     <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B552" t="inlineStr">
         <is>
           <t>Tres Valles</t>
@@ -7695,6 +10295,11 @@
       </c>
     </row>
     <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B553" t="inlineStr">
         <is>
           <t>Tuxpan</t>
@@ -7708,6 +10313,11 @@
       </c>
     </row>
     <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B554" t="inlineStr">
         <is>
           <t>Veracruz</t>
@@ -7721,6 +10331,11 @@
       </c>
     </row>
     <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B555" t="inlineStr">
         <is>
           <t>Xalapa</t>
@@ -7734,6 +10349,11 @@
       </c>
     </row>
     <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B556" t="inlineStr">
         <is>
           <t>Zongolica</t>
@@ -7747,6 +10367,11 @@
       </c>
     </row>
     <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B557" t="inlineStr">
         <is>
           <t>Total</t>
@@ -7778,6 +10403,11 @@
       </c>
     </row>
     <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>Yucatán</t>
+        </is>
+      </c>
       <c r="B559" t="inlineStr">
         <is>
           <t>Mérida</t>
@@ -7791,6 +10421,11 @@
       </c>
     </row>
     <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>Yucatán</t>
+        </is>
+      </c>
       <c r="B560" t="inlineStr">
         <is>
           <t>Total</t>
@@ -7822,6 +10457,11 @@
       </c>
     </row>
     <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B562" t="inlineStr">
         <is>
           <t>Chalchihuites</t>
@@ -7835,9 +10475,14 @@
       </c>
     </row>
     <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>Concepción del Oro</t>
+          <t>Concepción Del Oro</t>
         </is>
       </c>
       <c r="C563">
@@ -7848,6 +10493,11 @@
       </c>
     </row>
     <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B564" t="inlineStr">
         <is>
           <t>Cuauhtémoc</t>
@@ -7861,6 +10511,11 @@
       </c>
     </row>
     <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B565" t="inlineStr">
         <is>
           <t>Fresnillo</t>
@@ -7874,6 +10529,11 @@
       </c>
     </row>
     <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B566" t="inlineStr">
         <is>
           <t>Genaro Codina</t>
@@ -7887,6 +10547,11 @@
       </c>
     </row>
     <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B567" t="inlineStr">
         <is>
           <t>General Enrique Estrada</t>
@@ -7900,6 +10565,11 @@
       </c>
     </row>
     <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B568" t="inlineStr">
         <is>
           <t>General Francisco R. Murguía</t>
@@ -7913,6 +10583,11 @@
       </c>
     </row>
     <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B569" t="inlineStr">
         <is>
           <t>General Pánfilo Natera</t>
@@ -7926,6 +10601,11 @@
       </c>
     </row>
     <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B570" t="inlineStr">
         <is>
           <t>Guadalupe</t>
@@ -7939,6 +10619,11 @@
       </c>
     </row>
     <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B571" t="inlineStr">
         <is>
           <t>Huanusco</t>
@@ -7952,6 +10637,11 @@
       </c>
     </row>
     <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B572" t="inlineStr">
         <is>
           <t>Jalpa</t>
@@ -7965,6 +10655,11 @@
       </c>
     </row>
     <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B573" t="inlineStr">
         <is>
           <t>Jerez</t>
@@ -7978,9 +10673,14 @@
       </c>
     </row>
     <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>Jiménez del Teul</t>
+          <t>Jiménez Del Teul</t>
         </is>
       </c>
       <c r="C574">
@@ -7991,6 +10691,11 @@
       </c>
     </row>
     <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B575" t="inlineStr">
         <is>
           <t>Juan Aldama</t>
@@ -8004,6 +10709,11 @@
       </c>
     </row>
     <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B576" t="inlineStr">
         <is>
           <t>Loreto</t>
@@ -8017,6 +10727,11 @@
       </c>
     </row>
     <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B577" t="inlineStr">
         <is>
           <t>Miguel Auza</t>
@@ -8030,6 +10745,11 @@
       </c>
     </row>
     <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B578" t="inlineStr">
         <is>
           <t>Monte Escobedo</t>
@@ -8043,9 +10763,14 @@
       </c>
     </row>
     <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>Nochistlán de Mejía</t>
+          <t>Nochistlán De Mejía</t>
         </is>
       </c>
       <c r="C579">
@@ -8056,6 +10781,11 @@
       </c>
     </row>
     <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B580" t="inlineStr">
         <is>
           <t>Ojocaliente</t>
@@ -8069,6 +10799,11 @@
       </c>
     </row>
     <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B581" t="inlineStr">
         <is>
           <t>Pinos</t>
@@ -8082,6 +10817,11 @@
       </c>
     </row>
     <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B582" t="inlineStr">
         <is>
           <t>Río Grande</t>
@@ -8095,6 +10835,11 @@
       </c>
     </row>
     <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B583" t="inlineStr">
         <is>
           <t>Sain Alto</t>
@@ -8108,6 +10853,11 @@
       </c>
     </row>
     <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B584" t="inlineStr">
         <is>
           <t>Sombrerete</t>
@@ -8121,9 +10871,14 @@
       </c>
     </row>
     <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>Tlaltenango de Sánchez Román</t>
+          <t>Tlaltenango De Sánchez Román</t>
         </is>
       </c>
       <c r="C585">
@@ -8134,6 +10889,11 @@
       </c>
     </row>
     <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B586" t="inlineStr">
         <is>
           <t>Valparaíso</t>
@@ -8147,9 +10907,14 @@
       </c>
     </row>
     <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>Villa de Cos</t>
+          <t>Villa De Cos</t>
         </is>
       </c>
       <c r="C587">
@@ -8160,6 +10925,11 @@
       </c>
     </row>
     <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B588" t="inlineStr">
         <is>
           <t>Villa García</t>
@@ -8173,6 +10943,11 @@
       </c>
     </row>
     <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B589" t="inlineStr">
         <is>
           <t>Villa Hidalgo</t>
@@ -8186,6 +10961,11 @@
       </c>
     </row>
     <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B590" t="inlineStr">
         <is>
           <t>Villanueva</t>
@@ -8199,6 +10979,11 @@
       </c>
     </row>
     <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B591" t="inlineStr">
         <is>
           <t>Zacatecas</t>
@@ -8212,6 +10997,11 @@
       </c>
     </row>
     <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B592" t="inlineStr">
         <is>
           <t>Total</t>
@@ -8235,41 +11025,6 @@
       </c>
       <c r="D593">
         <v>1</v>
-      </c>
-    </row>
-    <row r="595">
-      <c r="B595" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 497,795</t>
-        </is>
-      </c>
-    </row>
-    <row r="596">
-      <c r="B596" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="597">
-      <c r="B597" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="598">
-      <c r="B598" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="599">
-      <c r="B599" t="inlineStr">
-        <is>
-          <t>Octubre de 2021</t>
-        </is>
       </c>
     </row>
   </sheetData>
